--- a/products.xlsx
+++ b/products.xlsx
@@ -1,110 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Languages\Python\Applications\POS\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEE34E9-CF04-4634-B2ED-E53923511084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Brand</t>
-  </si>
-  <si>
-    <t>Barcode</t>
-  </si>
-  <si>
-    <t>Cellphone</t>
-  </si>
-  <si>
-    <t>1110ADAS</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>iPhone</t>
-  </si>
-  <si>
-    <t>Piano XL | SD</t>
-  </si>
-  <si>
-    <t>SD12031415</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>8000</t>
-  </si>
-  <si>
-    <t>Platinum</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="IDAutomationHC39M Free Version"/>
-      <family val="1"/>
-      <charset val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,23 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -468,250 +396,170 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="7" max="7" width="14.625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G28"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="str">
-        <f>IF(B2="","", "*"&amp;B2&amp;"*")</f>
-        <v>*1110ADAS*</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1" t="str">
-        <f>IF(B3="","", "*"&amp;B3&amp;"*")</f>
-        <v>*SD12031415*</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G4" s="1" t="str">
-        <f t="shared" ref="G4:G30" si="0">IF(B4="","", "*"&amp;B4&amp;"*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="7:7" ht="72" x14ac:dyDescent="2.25">
-      <c r="G30" s="1" t="str">
-        <f t="shared" si="0"/>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>SKU</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Price</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Quantity</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Brand</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Barcode</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="G2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="G3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="G4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="G5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="G6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="G7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="G8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="G9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="G10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="G11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="G12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="G13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="G14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="G15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="G17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="G18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="G19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="G21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="G23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="G24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="G25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="G26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="G27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="G28" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1 A4:F19 A3:F3 A2 C2:F2" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G28"/>
   </ignoredErrors>
 </worksheet>
 </file>